--- a/src/test-data/test-data.xlsx
+++ b/src/test-data/test-data.xlsx
@@ -1,127 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\risk-desktop\test_data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B2B9B18-EDC3-423B-8159-393F3A71A967}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
     <sheet name="UI_TestData" sheetId="1" r:id="rId1"/>
     <sheet name="API_TestData" sheetId="2" r:id="rId2"/>
     <sheet name="ETL_TestData" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="31">
-  <si>
-    <t>TestCaseID</t>
-  </si>
-  <si>
-    <t>searchQuery</t>
-  </si>
-  <si>
-    <t>expectedTitle</t>
-  </si>
-  <si>
-    <t>TC001</t>
-  </si>
-  <si>
-    <t>Component</t>
-  </si>
-  <si>
-    <t>Angular</t>
-  </si>
-  <si>
-    <t>TC002</t>
-  </si>
-  <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>customer_id</t>
-  </si>
-  <si>
-    <t>endpoint</t>
-  </si>
-  <si>
-    <t>method</t>
-  </si>
-  <si>
-    <t>expectedStatus</t>
-  </si>
-  <si>
-    <t>dbCheck</t>
-  </si>
-  <si>
-    <t>/posts/1</t>
-  </si>
-  <si>
-    <t>GET</t>
-  </si>
-  <si>
-    <t>true</t>
-  </si>
-  <si>
-    <t>/posts/2</t>
-  </si>
-  <si>
-    <t>sourceFile</t>
-  </si>
-  <si>
-    <t>targetFile</t>
-  </si>
-  <si>
-    <t>primaryKey</t>
-  </si>
-  <si>
-    <t>aggregateField</t>
-  </si>
-  <si>
-    <t>aggregateType</t>
-  </si>
-  <si>
-    <t>expectedAggregateValue</t>
-  </si>
-  <si>
-    <t>test_data/source_etl.csv</t>
-  </si>
-  <si>
-    <t>test_data/target_etl.csv</t>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>balance</t>
-  </si>
-  <si>
-    <t>SUM</t>
-  </si>
-  <si>
-    <t>6200.50</t>
-  </si>
-  <si>
-    <t>Pawan</t>
-  </si>
-  <si>
-    <t>Dwivedi</t>
-  </si>
-</sst>
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
+  <fonts count="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -151,21 +67,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -490,206 +398,197 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="9.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.08203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.9140625" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" t="s">
-        <v>5</v>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>TestCaseID</v>
+      </c>
+      <c r="B1" t="str">
+        <v>searchQuery</v>
+      </c>
+      <c r="C1" t="str">
+        <v>expectedTitle</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>TC001</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Component</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Angular</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>TC002</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Signal</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Angular</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C3"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F3"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>TestCaseID</v>
+      </c>
+      <c r="B1" t="str">
+        <v>customer_id</v>
+      </c>
+      <c r="C1" t="str">
+        <v>endpoint</v>
+      </c>
+      <c r="D1" t="str">
+        <v>method</v>
+      </c>
+      <c r="E1" t="str">
+        <v>expectedStatus</v>
+      </c>
+      <c r="F1" t="str">
+        <v>dbCheck</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>TC001</v>
+      </c>
+      <c r="B2" t="str">
+        <v>TC001</v>
+      </c>
+      <c r="C2" t="str">
+        <v>/posts/1</v>
+      </c>
+      <c r="D2" t="str">
+        <v>GET</v>
+      </c>
+      <c r="E2">
+        <v>200</v>
+      </c>
+      <c r="F2" t="str">
+        <v>true</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>TC002</v>
+      </c>
+      <c r="B3" t="str">
+        <v>TC002</v>
+      </c>
+      <c r="C3" t="str">
+        <v>/posts/2</v>
+      </c>
+      <c r="D3" t="str">
+        <v>GET</v>
+      </c>
+      <c r="E3">
+        <v>200</v>
+      </c>
+      <c r="F3" t="str">
+        <v>true</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:C2 B3:C3" numberStoredAsText="1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F3"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G7"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2">
-        <v>200</v>
-      </c>
-      <c r="F2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3">
-        <v>200</v>
-      </c>
-      <c r="F3" t="s">
-        <v>15</v>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>TestCaseID</v>
+      </c>
+      <c r="B1" t="str">
+        <v>sourceFile</v>
+      </c>
+      <c r="C1" t="str">
+        <v>targetFile</v>
+      </c>
+      <c r="D1" t="str">
+        <v>primaryKey</v>
+      </c>
+      <c r="E1" t="str">
+        <v>aggregateField</v>
+      </c>
+      <c r="F1" t="str">
+        <v>aggregateType</v>
+      </c>
+      <c r="G1" t="str">
+        <v>expectedAggregateValue</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>TC001</v>
+      </c>
+      <c r="B2" t="str">
+        <v>test_data/source_etl.csv</v>
+      </c>
+      <c r="C2" t="str">
+        <v>test_data/target_etl.csv</v>
+      </c>
+      <c r="D2" t="str">
+        <v>id</v>
+      </c>
+      <c r="E2" t="str">
+        <v>balance</v>
+      </c>
+      <c r="F2" t="str">
+        <v>SUM</v>
+      </c>
+      <c r="G2" t="str">
+        <v>6200.50</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>TC001</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Pawan</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Angular</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>TC001</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Dwivedi</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Angular</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:F3" numberStoredAsText="1"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="A1:G2" numberStoredAsText="1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G7"/>
   </ignoredErrors>
 </worksheet>
 </file>